--- a/admin/public/imports/product/sv.xlsx
+++ b/admin/public/imports/product/sv.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos-1/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFCE01B-7820-FD47-B0A0-F6C11DE15226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25940" yWindow="6780" windowWidth="32860" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="21780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,63 +27,137 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>*Produktnamn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Tillhörande kategori
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（andra nivåns kategorier, vänligen separera med /）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Lagerberäkningsmetod
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Lagerminskning vid beställning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1/Lagerminskning vid betalning=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>*Produktenshet</t>
+  </si>
+  <si>
+    <t>*Specificeringsnamn</t>
+  </si>
+  <si>
+    <t>Bildnamn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Lagerantal
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（maximalt lager：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>99999999</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
   <si>
     <t xml:space="preserve">	
 Produktstreckkod</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>*Produktpris</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>*Platsmålgivningsskatt</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Takeaway-skatt</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Produktordning</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>*Produktnamn</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>*Produktenshet</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>*Specificeringsnamn</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bildnamn</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*Produktstatus
@@ -100,7 +168,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>（Hylla</t>
@@ -110,7 +177,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>=1/Avhylla=0</t>
@@ -120,23 +187,63 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+  </si>
+  <si>
+    <t>*Platsmålgivningsskatt</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Takeaway-skatt</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">*Lagerberäkningsmetod
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Prisberäkningsmetod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -144,39 +251,264 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（Lagerminskning vid beställning</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Heltalsprisberäkning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>=1/Lagerminskning vid betalning=2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，Decimalprisberäkning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dessert/Hongkong-dessert</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Visa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Flera val möjliga, visa eller inte：Kassapost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1/Tablet=2/Köksbildskärm=3/Beställningsassistent=4/Scan och beställ=5/Utleverans=6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Observera: När prissättningsmetoden är 2 kan det bara visas upp till：Kassapost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1/Köksbildskärm3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>Produktordning</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Maxantal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（0 betyder ingen köpbegränsning）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*medlemsrabatt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Aktivera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/Stäng=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*Rabatt på hela beställningen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Aktivera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/Stäng=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">(exempel, vänligen ta bort denna rad vid import)
 English:Caramel pudding
 </t>
@@ -186,7 +518,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
-        <family val="2"/>
         <charset val="222"/>
       </rPr>
       <t>ภาษาไทย</t>
@@ -196,7 +527,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -206,7 +536,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
-        <family val="2"/>
         <charset val="222"/>
       </rPr>
       <t>พุดดิ้งคาราเมล</t>
@@ -216,7 +545,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -227,7 +555,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>简体中文</t>
@@ -237,7 +564,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -247,7 +573,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>焦糖布丁</t>
@@ -257,7 +582,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -268,7 +592,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>繁體中文</t>
@@ -278,7 +601,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -288,7 +610,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>焦糖布丁</t>
@@ -298,7 +619,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -310,7 +630,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Myanmar Text"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>မြန်မာဘာသာ</t>
     </r>
@@ -319,7 +639,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -329,7 +648,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Myanmar Text"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ရွှင်ဆူမန်</t>
     </r>
@@ -338,7 +657,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -349,7 +667,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>日本語</t>
@@ -359,7 +676,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -369,7 +685,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
         <charset val="128"/>
       </rPr>
       <t>クレームブリュレ</t>
@@ -379,7 +694,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -390,7 +704,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Malgun Gothic"/>
-        <family val="2"/>
         <charset val="129"/>
       </rPr>
       <t>한국어</t>
@@ -400,7 +713,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>:</t>
@@ -410,7 +722,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Malgun Gothic"/>
-        <family val="2"/>
         <charset val="129"/>
       </rPr>
       <t>크림</t>
@@ -420,7 +731,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -430,7 +740,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Malgun Gothic"/>
-        <family val="2"/>
         <charset val="129"/>
       </rPr>
       <t>브륄레</t>
@@ -440,355 +749,37 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 Svenska:Karamellpudding</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dessert/Hongkong-dessert</t>
+  </si>
+  <si>
+    <t>stycken</t>
   </si>
   <si>
     <t>Alkoholhaltiga drycker</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>stycken</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*medlemsrabatt
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（Aktivera</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>=1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/Stäng=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*Lagerantal
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（maximalt lager：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>99999999</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*Tillhörande kategori
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（andra nivåns kategorier, vänligen separera med /）</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Prisberäkningsmetod</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（Heltalsprisberäkning</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，Decimalprisberäkning</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Maxantal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（0 betyder ingen köpbegränsning）</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">*Visa
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（Flera val möjliga, visa eller inte：Kassapost</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=1/Tablet=2/Köksbildskärm=3/Beställningsassistent=4/Scan och beställ=5/Utleverans=6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（Observera: När prissättningsmetoden är 2 kan det bara visas upp till：Kassapost</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1/Köksbildskärm3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -796,105 +787,423 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体-简"/>
-      <family val="1"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
       <charset val="222"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Myanmar Text"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -902,55 +1211,335 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1160,102 +1749,106 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1397058823529" style="2" customWidth="1"/>
     <col min="5" max="5" width="11" style="2" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="27.7109375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="12.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="29.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.8529411764706" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.4264705882353" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.5735294117647" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
+    <col min="11" max="12" width="12.7132352941176" style="2" customWidth="1"/>
+    <col min="13" max="13" width="29.7132352941176" style="1" customWidth="1"/>
     <col min="14" max="14" width="62" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16.85546875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.8529411764706" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.4044117647059" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="95" customHeight="1">
+    <row r="1" ht="95" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="194" spans="1:18">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="202">
-      <c r="A2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>14</v>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G2" s="2">
         <v>9999</v>
@@ -1266,11 +1859,11 @@
       <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>13</v>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
@@ -1287,21 +1880,24 @@
       <c r="Q2" s="1">
         <v>1</v>
       </c>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A3" s="7"/>
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A3" s="5"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="K4" s="3"/>
+    <row r="4" spans="1:11">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/admin/public/imports/product/sv.xlsx
+++ b/admin/public/imports/product/sv.xlsx
@@ -775,7 +775,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -792,13 +792,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -958,6 +951,12 @@
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -971,12 +970,6 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1314,148 +1307,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1469,19 +1462,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/admin/public/imports/product/sv.xlsx
+++ b/admin/public/imports/product/sv.xlsx
@@ -157,6 +157,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">*Visa
 </t>
     </r>
@@ -1322,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="4">
-        <v>1234567</v>
+        <v>123456</v>
       </c>
       <c r="M2" s="4">
         <v>1</v>

--- a/admin/public/imports/product/sv.xlsx
+++ b/admin/public/imports/product/sv.xlsx
@@ -27,39 +27,267 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
-  <si>
-    <t>*Namn</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>*Produktnamn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Tillhörande kategori
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（andra nivåns kategorier, vänligen separera med /）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Lagerberäkningsmetod
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Lagerminskning vid beställning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1/Lagerminskning vid betalning=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>*Produktenshet</t>
+  </si>
+  <si>
+    <t>*Specificeringsnamn</t>
+  </si>
+  <si>
+    <t>Bildnamn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Lagerantal
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（maximalt lager：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>99999999</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Produktstreckkod</t>
+  </si>
+  <si>
+    <t>*Produktpris</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*Produktstatus
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Hylla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1/Avhylla=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>*Platsmålgivningsskatt</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">*Kategori
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Takeaway-skatt</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Prisberäkningsmetod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>andra nivåns kategorier, vänligen separera med /</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Heltalsprisberäkning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，Decimalprisberäkning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
@@ -67,173 +295,72 @@
     </r>
   </si>
   <si>
-    <t>*Enhet</t>
-  </si>
-  <si>
-    <t>*Specifikation</t>
-  </si>
-  <si>
-    <t>*Pris</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">*Prissättningsmetod </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(heltal=1/decimal=2)</t>
-    </r>
-  </si>
-  <si>
-    <t>Streckkod</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">*Publicera </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Aktivera=1/Stäng=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>*Platsmålgivningsskatt</t>
-  </si>
-  <si>
-    <t>*Takeaway-skatt</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">*Lageravdrag
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t> (vid beställning=1/vid betalning=2)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
+    <r>
       <t xml:space="preserve">*Visa
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Flera val möjliga, visa eller inte</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Kassapost=1/Tablet=2/Köksbildskärm=3/Beställningsassistent=4/Bordskod beställ=5/Skanna beställ=6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Flera val möjliga, visa eller inte：Kassapost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=1/Tablet=2/Köksbildskärm=3/Beställningsassistent=4/Bordskod beställ=5/Skanna beställ=6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*medlemsrabatt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Aktivera=1/Stäng=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Observera: När prissättningsmetoden är 2 kan det bara visas upp till：Kassapost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1/Köksbildskärm3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
@@ -241,11 +368,97 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
+    <t>Produktordning</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Maxantal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（0 betyder ingen köpbegränsning）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*medlemsrabatt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Aktivera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/Stäng=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*Rabatt på hela beställningen
 </t>
@@ -253,48 +466,300 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（Aktivera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/Stäng=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Aktivera=1/Stäng=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>(exempel, vänligen ta bort denna rad vid import)
- English:Caramel pudding
- ภาษาไทย:พุดดิ้งคาราเมล
- 简体中文:焦糖布丁
- 繁體中文:焦糖布丁
- Türkçe:crème brûlée
- မြန်မာဘာသာ:ရွှင်ဆူမန်
- 日本語:クレームブリュレ
- 한국어:크림 브륄레
+      <t xml:space="preserve">(exempel, vänligen ta bort denna rad vid import)
+English:Caramel pudding
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ภาษาไทย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="222"/>
+      </rPr>
+      <t>พุดดิ้งคาราเมล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简体中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁體中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+Türkçe:crème brûlée
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Myanmar Text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>မြန်မာဘာသာ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Myanmar Text"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ရွှင်ဆူမန်</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本語</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="128"/>
+      </rPr>
+      <t>クレームブリュレ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <charset val="129"/>
+      </rPr>
+      <t>브륄레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Svenska:Karamellpudding</t>
+    </r>
   </si>
   <si>
     <t>Dessert/Hongkong-dessert</t>
   </si>
   <si>
     <t>stycken</t>
-  </si>
-  <si>
-    <t>Standard</t>
   </si>
   <si>
     <t>Alkoholhaltiga drycker</t>
@@ -310,7 +775,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -320,12 +785,20 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -481,13 +954,52 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Myanmar Text"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="33">
@@ -795,172 +1307,175 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1233,108 +1748,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="1"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="25.2867647058824" customWidth="1"/>
-    <col min="2" max="2" width="24.8529411764706" customWidth="1"/>
-    <col min="3" max="3" width="11.1397058823529" customWidth="1"/>
-    <col min="4" max="4" width="12.7132352941176" customWidth="1"/>
-    <col min="6" max="6" width="17.7132352941176" customWidth="1"/>
-    <col min="8" max="8" width="19.5735294117647" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="21.1397058823529" customWidth="1"/>
-    <col min="11" max="11" width="22.2867647058824" customWidth="1"/>
-    <col min="12" max="12" width="54.4264705882353" customWidth="1"/>
-    <col min="13" max="13" width="20.2867647058824" customWidth="1"/>
-    <col min="14" max="14" width="24.1397058823529" customWidth="1"/>
+    <col min="1" max="1" width="32" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1397058823529" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.8529411764706" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.4264705882353" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.5735294117647" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
+    <col min="11" max="12" width="12.7132352941176" style="2" customWidth="1"/>
+    <col min="13" max="13" width="29.7132352941176" style="1" customWidth="1"/>
+    <col min="14" max="14" width="62" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.8529411764706" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.4044117647059" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="81" customHeight="1" spans="1:14">
+    <row r="1" ht="95" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="197.25" customHeight="1" spans="1:14">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="4">
+    <row r="2" ht="194" spans="1:18">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2">
+        <v>9999</v>
+      </c>
+      <c r="I2" s="2">
         <v>50</v>
       </c>
-      <c r="F2" s="4">
+      <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4">
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>123456</v>
+      </c>
+      <c r="O2" s="1">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="4">
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>1</v>
       </c>
-      <c r="L2" s="4">
-        <v>123456</v>
-      </c>
-      <c r="M2" s="4">
+      <c r="R2" s="1">
         <v>1</v>
       </c>
-      <c r="N2" s="4">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A3" s="5"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
